--- a/config/gln.xlsx
+++ b/config/gln.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smmnoor\Documents\Drug inventory system\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smmnoor\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08CC06D3-A00F-42A6-A8EB-6181B61F1394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696C02E7-5160-4971-8A25-A9DD0D2F5ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A19A7C7B-1FE4-429F-8237-AC97BD1C4977}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>GLN</t>
   </si>
@@ -129,6 +129,9 @@
   </si>
   <si>
     <t>To Address</t>
+  </si>
+  <si>
+    <t>MOH - NAJRAN</t>
   </si>
 </sst>
 </file>
@@ -528,7 +531,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDE07732-F0FF-4A65-9527-F1ACC573B7FA}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.625" style="4" customWidth="1"/>
@@ -765,14 +768,22 @@
         <v>6286844000114</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
+        <v>6286844000114</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
         <v>9999999999999</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B31" s="2" t="s">
         <v>29</v>
       </c>
     </row>
